--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.08164865225012</v>
+        <v>7.000767905990645</v>
       </c>
       <c r="D2" t="n">
-        <v>43.35001281558185</v>
+        <v>7.04437708253205</v>
       </c>
       <c r="E2" t="n">
-        <v>7.586868184382777</v>
+        <v>1.232866079962201</v>
       </c>
       <c r="F2" t="n">
-        <v>5.763433761262426</v>
+        <v>0.9365579862051442</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.66547954010058</v>
+        <v>10.02064042526635</v>
       </c>
       <c r="D3" t="n">
-        <v>57.23179461792142</v>
+        <v>9.300166625412231</v>
       </c>
       <c r="E3" t="n">
-        <v>7.586868184382777</v>
+        <v>1.232866079962201</v>
       </c>
       <c r="F3" t="n">
-        <v>5.763433761262426</v>
+        <v>0.9365579862051442</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.31455595072384</v>
+        <v>8.501115341992623</v>
       </c>
       <c r="D4" t="n">
-        <v>52.51561936964828</v>
+        <v>8.533788147567845</v>
       </c>
       <c r="E4" t="n">
-        <v>7.586868184382777</v>
+        <v>1.232866079962201</v>
       </c>
       <c r="F4" t="n">
-        <v>5.763433761262426</v>
+        <v>0.9365579862051442</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
